--- a/education_forms/036_feudalism_and_empire_analysis--education_forms.xlsx
+++ b/education_forms/036_feudalism_and_empire_analysis--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>feudalism_and_empire_analysis</t>
+          <t>feudalism_and_empire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feudal-systems-and-empires</t>
+          <t>Feudalism and Empire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>empires</t>
+          <t>Emperies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>feudalism_and_empires_relationship</t>
+          <t>relationship_between_feudalism_and_empires</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>relationship-between-feudalism-and-empires</t>
+          <t>Relationship between Feudalism and Empires</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>impact_of_feudalism_and_empires</t>
+          <t>impact_feudalism_and_empires</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>impact-of-feudalism-and-empires</t>
+          <t>Impact of Feudalism and Empires</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submit_button</t>
+          <t>submit_note</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submit Note</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,63 +630,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>user_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>User Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Select Multiple</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Select One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select-one</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,345 +745,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>submit_note_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select-multiple</t>
+          <t>Submit Note 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>select-one</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>select-multiple</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>select-one</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>select-multiple</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1165,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rome</t>
+          <t>sui_dynasty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Sui Dynasty</t>
         </is>
       </c>
     </row>
@@ -1182,420 +883,148 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sui_dynasty</t>
+          <t>han_dynasty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sui Dynasty</t>
+          <t>Han Dynasty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>empires_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>han_dynasty</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Han Dynasty</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>second</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>third</t>
+          <t>option_d</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>option_e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Option E</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>option_f</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Option F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>option_g</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gamma</t>
+          <t>Option G</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>option_h</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Delta</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_d</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_e</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option E</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_f</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option F</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_g</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option G</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_h</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>Option H</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_i</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option I</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option_j</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Option J</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_k</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option K</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option_l</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Option L</t>
         </is>
       </c>
     </row>
